--- a/data/trans_orig/P57C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha sido optimista respecto a su futuro en 2023</t>
+          <t>Población según si ha sido optimista respecto a su futuro en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36914</t>
+          <t>37299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>38919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61284</t>
+          <t>61419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55186</t>
+          <t>55091</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40534</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59055</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76690</t>
+          <t>77066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106423</t>
+          <t>108210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70205</t>
+          <t>71928</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103824</t>
+          <t>105806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>95981</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>124293</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>175334</t>
+          <t>175437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>219209</t>
+          <t>219108</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>231759</t>
+          <t>236831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285390</t>
+          <t>287798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270408</t>
+          <t>270639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>311931</t>
+          <t>312665</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>518103</t>
+          <t>516922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>584524</t>
+          <t>585453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197114</t>
+          <t>195457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252313</t>
+          <t>253960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176626</t>
+          <t>175862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216654</t>
+          <t>216625</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>388651</t>
+          <t>386458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459845</t>
+          <t>454572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37148</t>
+          <t>36247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56508</t>
+          <t>56025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>24479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70550</t>
+          <t>69940</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65208</t>
+          <t>65614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90307</t>
+          <t>89840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85989</t>
+          <t>86759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152410</t>
+          <t>150910</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56586</t>
+          <t>48449</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>142488</t>
+          <t>138214</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137406</t>
+          <t>136691</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175532</t>
+          <t>173775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175984</t>
+          <t>175137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>300568</t>
+          <t>303565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230163</t>
+          <t>204513</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>554545</t>
+          <t>552086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>389022</t>
+          <t>389476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>440687</t>
+          <t>439861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>575269</t>
+          <t>545880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>964964</t>
+          <t>968628</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>423880</t>
+          <t>428497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862107</t>
+          <t>906336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256465</t>
+          <t>258639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308818</t>
+          <t>309231</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702301</t>
+          <t>700859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1273334</t>
+          <t>1337586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>17644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32906</t>
+          <t>33491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>16114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51967</t>
+          <t>54517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34772</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78060</t>
+          <t>76635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54198</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91991</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39999</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>108718</t>
+          <t>112256</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>98884</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>185795</t>
+          <t>183379</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>322868</t>
+          <t>320331</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>382603</t>
+          <t>381555</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>464298</t>
+          <t>462092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>755884</t>
+          <t>769809</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>812616</t>
+          <t>812775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1221723</t>
+          <t>1188418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216333</t>
+          <t>219101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276349</t>
+          <t>279471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105602</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>306357</t>
+          <t>304724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>285156</t>
+          <t>308976</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>561807</t>
+          <t>560889</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>32466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52540</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38742</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65551</t>
+          <t>63630</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53735</t>
+          <t>51675</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84572</t>
+          <t>82346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>99846</t>
+          <t>98557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>140604</t>
+          <t>138782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121670</t>
+          <t>122603</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>166044</t>
+          <t>165503</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>138270</t>
+          <t>139703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>199500</t>
+          <t>201096</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277083</t>
+          <t>276101</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>352144</t>
+          <t>351191</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>400941</t>
+          <t>398991</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>466424</t>
+          <t>464456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>347709</t>
+          <t>352254</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>478639</t>
+          <t>477213</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>769903</t>
+          <t>775175</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>925031</t>
+          <t>924157</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>250628</t>
+          <t>253767</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>315604</t>
+          <t>317575</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>328743</t>
+          <t>328543</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>545907</t>
+          <t>527507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>605327</t>
+          <t>602688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>840725</t>
+          <t>821392</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>48274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>82600</t>
+          <t>83137</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>65137</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>124891</t>
+          <t>124827</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>175927</t>
+          <t>179840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>126441</t>
+          <t>126789</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>193993</t>
+          <t>192566</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>181360</t>
+          <t>183988</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>254479</t>
+          <t>257403</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>332625</t>
+          <t>338427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>432127</t>
+          <t>435654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>316511</t>
+          <t>311671</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>454903</t>
+          <t>452641</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>421735</t>
+          <t>414207</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>571656</t>
+          <t>572000</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>796888</t>
+          <t>816696</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>999056</t>
+          <t>1004693</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1160894</t>
+          <t>1150978</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1611729</t>
+          <t>1609754</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1576924</t>
+          <t>1583768</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2104043</t>
+          <t>2136869</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2882394</t>
+          <t>2898143</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3524172</t>
+          <t>3529577</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1166794</t>
+          <t>1164569</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1807822</t>
+          <t>1794774</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>911991</t>
+          <t>925272</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1240325</t>
+          <t>1232117</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2183899</t>
+          <t>2188436</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2959149</t>
+          <t>2952345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20347</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29538</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>48965</t>
+          <t>52850</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38919</t>
+          <t>41134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61419</t>
+          <t>66828</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55091</t>
+          <t>56816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49286</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>64171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91344</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77066</t>
+          <t>81858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108210</t>
+          <t>115105</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86087</t>
+          <t>93730</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>76609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105806</t>
+          <t>113564</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109403</t>
+          <t>120028</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>104455</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>134753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>195490</t>
+          <t>213758</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>175437</t>
+          <t>190306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>219108</t>
+          <t>240209</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>261299</t>
+          <t>281448</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236831</t>
+          <t>251416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287798</t>
+          <t>308980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289989</t>
+          <t>310806</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270639</t>
+          <t>289009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>312665</t>
+          <t>334908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>551288</t>
+          <t>592254</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>516922</t>
+          <t>556376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>585453</t>
+          <t>626309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>223734</t>
+          <t>246658</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195457</t>
+          <t>218231</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253960</t>
+          <t>278339</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>196944</t>
+          <t>218363</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175862</t>
+          <t>195972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216625</t>
+          <t>242851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>420678</t>
+          <t>465021</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386458</t>
+          <t>431229</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454572</t>
+          <t>502941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>633524</t>
+          <t>688707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>633524</t>
+          <t>688707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633524</t>
+          <t>688707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>674240</t>
+          <t>731580</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>674240</t>
+          <t>731580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>674240</t>
+          <t>731580</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1307764</t>
+          <t>1420287</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1307764</t>
+          <t>1420287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1307764</t>
+          <t>1420287</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25105</t>
+          <t>26890</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>39670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41409</t>
+          <t>44685</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>34389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56025</t>
+          <t>61521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50206</t>
+          <t>53379</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69940</t>
+          <t>69947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76165</t>
+          <t>86075</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89840</t>
+          <t>101567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>126372</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>121014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150910</t>
+          <t>161488</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>104388</t>
+          <t>115952</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>97912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138214</t>
+          <t>138524</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154327</t>
+          <t>175257</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>136691</t>
+          <t>154546</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>173775</t>
+          <t>196658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>258714</t>
+          <t>291209</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175137</t>
+          <t>263284</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303565</t>
+          <t>321810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>427811</t>
+          <t>467636</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204513</t>
+          <t>433703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>552086</t>
+          <t>501086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>415138</t>
+          <t>464268</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>389476</t>
+          <t>433516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>439861</t>
+          <t>491540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>842950</t>
+          <t>931904</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>545880</t>
+          <t>886548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>968628</t>
+          <t>982478</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>594155</t>
+          <t>394154</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>428497</t>
+          <t>358404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>906336</t>
+          <t>432099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>283894</t>
+          <t>314681</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258639</t>
+          <t>288391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309231</t>
+          <t>345940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>878049</t>
+          <t>708835</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700859</t>
+          <t>666131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337586</t>
+          <t>757620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>954629</t>
+          <t>1067171</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>954629</t>
+          <t>1067171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>954629</t>
+          <t>1067171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2147494</t>
+          <t>2116088</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2147494</t>
+          <t>2116088</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2147494</t>
+          <t>2116088</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>20700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>29812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>24113</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33491</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>27922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54517</t>
+          <t>54119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>55514</t>
+          <t>62765</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>48499</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76635</t>
+          <t>81059</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71180</t>
+          <t>78881</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>62083</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>100950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80058</t>
+          <t>87344</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112256</t>
+          <t>104158</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>151239</t>
+          <t>166226</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>98884</t>
+          <t>144411</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>183379</t>
+          <t>192830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>351260</t>
+          <t>393672</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>320331</t>
+          <t>358236</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>381555</t>
+          <t>426167</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>581682</t>
+          <t>399726</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>462092</t>
+          <t>373563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>769809</t>
+          <t>425942</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>932943</t>
+          <t>793398</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>812775</t>
+          <t>752031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1188418</t>
+          <t>830846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>247325</t>
+          <t>293436</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219101</t>
+          <t>260046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>279471</t>
+          <t>327932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>227288</t>
+          <t>273690</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105357</t>
+          <t>250482</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>304724</t>
+          <t>302631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>474614</t>
+          <t>567126</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308976</t>
+          <t>526899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>560889</t>
+          <t>605955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>702936</t>
+          <t>801211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>702936</t>
+          <t>801211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>702936</t>
+          <t>801211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>928866</t>
+          <t>806954</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>928866</t>
+          <t>806954</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>928866</t>
+          <t>806954</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1631803</t>
+          <t>1608165</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1631803</t>
+          <t>1608165</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1631803</t>
+          <t>1608165</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>40975</t>
+          <t>46183</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31736</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55303</t>
+          <t>60606</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50185</t>
+          <t>53057</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63630</t>
+          <t>67747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68338</t>
+          <t>74681</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51675</t>
+          <t>63056</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82346</t>
+          <t>89333</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>118524</t>
+          <t>127738</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>98557</t>
+          <t>109317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138782</t>
+          <t>147711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -2997,22 +2997,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>142792</t>
+          <t>153949</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>122603</t>
+          <t>131009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>165503</t>
+          <t>178863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>176401</t>
+          <t>195348</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139703</t>
+          <t>172222</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201096</t>
+          <t>218044</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>319193</t>
+          <t>349297</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276101</t>
+          <t>318358</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>351191</t>
+          <t>378888</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>432363</t>
+          <t>454529</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>398991</t>
+          <t>422797</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>464456</t>
+          <t>488945</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>439352</t>
+          <t>479144</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>352254</t>
+          <t>451553</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>477213</t>
+          <t>506099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>871715</t>
+          <t>933673</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>775175</t>
+          <t>887344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>924157</t>
+          <t>976075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>281581</t>
+          <t>306519</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>253767</t>
+          <t>271933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>317575</t>
+          <t>338443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>386132</t>
+          <t>340534</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>328543</t>
+          <t>313124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>527507</t>
+          <t>369793</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>667713</t>
+          <t>647053</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>602688</t>
+          <t>603361</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>821392</t>
+          <t>689286</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925194</t>
+          <t>988518</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925194</t>
+          <t>988518</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925194</t>
+          <t>988518</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1092926</t>
+          <t>1115425</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1092926</t>
+          <t>1115425</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1092926</t>
+          <t>1115425</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2018120</t>
+          <t>2103943</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2018120</t>
+          <t>2103943</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2018120</t>
+          <t>2103943</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>91123</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>83569</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65137</t>
+          <t>75545</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>101700</t>
+          <t>108369</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>148842</t>
+          <t>162368</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>124827</t>
+          <t>142048</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>179840</t>
+          <t>188852</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>165270</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>126789</t>
+          <t>151211</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>192566</t>
+          <t>198556</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>226484</t>
+          <t>251908</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>183988</t>
+          <t>227786</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>257403</t>
+          <t>278136</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>391753</t>
+          <t>426361</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>338427</t>
+          <t>389884</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>435654</t>
+          <t>460634</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>404447</t>
+          <t>442512</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>311671</t>
+          <t>406330</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>452641</t>
+          <t>484479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>520189</t>
+          <t>577978</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>414207</t>
+          <t>540352</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>572000</t>
+          <t>619720</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>924636</t>
+          <t>1020490</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>816696</t>
+          <t>967213</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1004693</t>
+          <t>1081329</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1472734</t>
+          <t>1597285</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1150978</t>
+          <t>1537246</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1609754</t>
+          <t>1665747</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1726162</t>
+          <t>1653945</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1583768</t>
+          <t>1603071</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2136869</t>
+          <t>1708570</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>3198895</t>
+          <t>3251230</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2898143</t>
+          <t>3173730</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3529577</t>
+          <t>3337507</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1346795</t>
+          <t>1240767</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1164569</t>
+          <t>1181856</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1794774</t>
+          <t>1302138</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1094259</t>
+          <t>1147268</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>925272</t>
+          <t>1096127</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1232117</t>
+          <t>1203147</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2441053</t>
+          <t>2388036</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2188436</t>
+          <t>2300544</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2952345</t>
+          <t>2471910</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3454518</t>
+          <t>3527354</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3650662</t>
+          <t>3721130</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7105180</t>
+          <t>7248484</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
